--- a/golf_streamlit/data/runder/Runde_202502_03.xlsx
+++ b/golf_streamlit/data/runder/Runde_202502_03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c624kh1\Documents\My Projects\golf_streamlit V2\data\runder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c624kh1\Documents\My Projects\min_git\golf_streamlit\data\runder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2340486B-169C-43EB-9803-7326644C4783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12288B0-0CED-426C-8477-46115AAD28A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="492" yWindow="456" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -478,12 +478,25 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="N2" s="2"/>
@@ -496,12 +509,25 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2">
+        <v>7</v>
+      </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="N3" s="2"/>
@@ -514,12 +540,25 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2">
+        <v>4</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="N4" s="2"/>
@@ -532,12 +571,25 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="N5" s="2"/>
@@ -550,12 +602,25 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>6</v>
+      </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="N6" s="2"/>
@@ -568,12 +633,25 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="N7" s="2"/>
@@ -586,12 +664,25 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="N8" s="2"/>
@@ -604,12 +695,25 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2">
+        <v>3</v>
+      </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="N9" s="2"/>
@@ -622,14 +726,29 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -640,14 +759,29 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2">
+        <v>5</v>
+      </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2">
+        <v>6</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="2"/>
@@ -658,14 +792,29 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2">
+        <v>6</v>
+      </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2">
+        <v>6</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -676,14 +825,29 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2">
+        <v>4</v>
+      </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2">
+        <v>7</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
@@ -694,14 +858,29 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>4</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
@@ -712,14 +891,29 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
@@ -730,14 +924,29 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
@@ -748,14 +957,29 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
@@ -766,14 +990,29 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2">
+        <v>6</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
@@ -784,12 +1023,25 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2">
+        <v>7</v>
+      </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2">
+        <v>7</v>
+      </c>
+      <c r="F19" s="2">
+        <v>5</v>
+      </c>
+      <c r="G19" s="2">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>7</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="N19" s="2"/>
